--- a/04 Ressourcen/Sport/Klassenlisten/Klassenliste Sport Vorlage.xlsx
+++ b/04 Ressourcen/Sport/Klassenlisten/Klassenliste Sport Vorlage.xlsx
@@ -120,9 +120,15 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -504,13 +510,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -522,42 +528,30 @@
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Klasse:</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>z. B. 7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Lehrkraft:</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>z. B. Klein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Lehrkraft:</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>z. B. Klein</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
           <t>Schuljahr:</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C2" s="2" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>z. B. 2026/27</t>
         </is>
@@ -581,60 +575,65 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>Klasse</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Note 1</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Note 2</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Note 3</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Note 4</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Note 5</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Note 6</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Note 7</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Note 8</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Note 9</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Note 10</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Note 12</t>
         </is>
@@ -658,6 +657,7 @@
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -677,6 +677,7 @@
       <c r="M6" s="7" t="n"/>
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="7" t="n"/>
+      <c r="P6" s="7" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -696,6 +697,7 @@
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
       <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -715,6 +717,7 @@
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -734,6 +737,7 @@
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -753,6 +757,7 @@
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="7" t="n"/>
+      <c r="P10" s="7" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -772,6 +777,7 @@
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -791,6 +797,7 @@
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
+      <c r="P12" s="7" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -810,6 +817,7 @@
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -829,6 +837,7 @@
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -848,6 +857,7 @@
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -867,6 +877,7 @@
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="7" t="n"/>
+      <c r="P16" s="7" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -886,6 +897,7 @@
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -905,6 +917,7 @@
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="7" t="n"/>
+      <c r="P18" s="7" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -924,6 +937,7 @@
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -943,6 +957,7 @@
       <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n"/>
       <c r="O20" s="7" t="n"/>
+      <c r="P20" s="7" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="5" t="n">
@@ -962,6 +977,7 @@
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -981,6 +997,7 @@
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="7" t="n"/>
+      <c r="P22" s="7" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="5" t="n">
@@ -1000,6 +1017,7 @@
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -1019,6 +1037,7 @@
       <c r="M24" s="7" t="n"/>
       <c r="N24" s="7" t="n"/>
       <c r="O24" s="7" t="n"/>
+      <c r="P24" s="7" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="5" t="n">
@@ -1038,6 +1057,7 @@
       <c r="M25" s="5" t="n"/>
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -1057,6 +1077,7 @@
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="7" t="n"/>
+      <c r="P26" s="7" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="5" t="n">
@@ -1076,6 +1097,7 @@
       <c r="M27" s="5" t="n"/>
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -1095,6 +1117,7 @@
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="7" t="n"/>
+      <c r="P28" s="7" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="5" t="n">
@@ -1114,6 +1137,7 @@
       <c r="M29" s="5" t="n"/>
       <c r="N29" s="5" t="n"/>
       <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -1133,6 +1157,7 @@
       <c r="M30" s="7" t="n"/>
       <c r="N30" s="7" t="n"/>
       <c r="O30" s="7" t="n"/>
+      <c r="P30" s="7" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="5" t="n">
@@ -1152,6 +1177,7 @@
       <c r="M31" s="5" t="n"/>
       <c r="N31" s="5" t="n"/>
       <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -1171,6 +1197,7 @@
       <c r="M32" s="7" t="n"/>
       <c r="N32" s="7" t="n"/>
       <c r="O32" s="7" t="n"/>
+      <c r="P32" s="7" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="5" t="n">
@@ -1190,6 +1217,7 @@
       <c r="M33" s="5" t="n"/>
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -1209,11 +1237,12 @@
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n"/>
       <c r="O34" s="7" t="n"/>
+      <c r="P34" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Ausfüllen: gelbe Felder oben (Klasse, Lehrkraft, Schuljahr) sowie Vorname und Nachname je Zeile.</t>
+          <t>Ausfüllen: gelbe Felder oben (Lehrkraft, Schuljahr) sowie Vorname, Nachname und Klasse je Zeile.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1263,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Beispielzeile (nur zur Ansicht, nicht Teil der Klasse):</t>
+          <t>Beispielzeile (nur zur Ansicht, nicht Teil des Kurses):</t>
         </is>
       </c>
     </row>
@@ -1252,44 +1281,53 @@
           <t>Mustermann</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>7b</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="10" t="n">
+      <c r="F40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="G40" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>2</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="10" t="n">
+      <c r="K40" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="K40" s="10" t="n">
-        <v>2</v>
       </c>
       <c r="L40" s="10" t="n">
         <v>2</v>
       </c>
       <c r="M40" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="10" t="n">
+      <c r="O40" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="O40" s="10" t="n">
+      <c r="P40" s="10" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/04 Ressourcen/Sport/Klassenlisten/Klassenliste Sport Vorlage.xlsx
+++ b/04 Ressourcen/Sport/Klassenlisten/Klassenliste Sport Vorlage.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,30 +36,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00999999"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,7 +55,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="0017453A"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,11 +66,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -126,10 +103,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,11 +114,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -538,11 +507,6 @@
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>z. B. Klein</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -550,778 +514,693 @@
           <t>Schuljahr:</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>z. B. 2026/27</t>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026/27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Nr.</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Vorname</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Nachname</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Klasse</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Note 1</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Note 2</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Note 3</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Note 4</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Note 5</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Note 6</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Note 7</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Note 8</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Note 9</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Note 10</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Note 12</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
-      <c r="P12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
-      <c r="P22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="7" t="n"/>
-      <c r="P24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n"/>
-      <c r="O26" s="7" t="n"/>
-      <c r="P26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="7" t="n"/>
-      <c r="P28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="6" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
-      <c r="P30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
-      <c r="K32" s="7" t="n"/>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="7" t="n"/>
-      <c r="P32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
-      <c r="P34" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Ausfüllen: gelbe Felder oben (Lehrkraft, Schuljahr) sowie Vorname, Nachname und Klasse je Zeile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Nummern 1–30 sind fest vergeben. Zeilen wechseln weiß / grau, damit die Note in der richtigen Zeile landet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Die Spalten Note 1–12 pro Einheit selbst benennen (Doppelklick auf die Kopfzeile), dann Noten eintragen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Beispielzeile (nur zur Ansicht, nicht Teil des Kurses):</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Mustermann</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>7b</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P40" s="10" t="n">
-        <v>3</v>
-      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
